--- a/data/trans_orig/IP16A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6872</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28550</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>55027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60762</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33200</t>
+          <t>33242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39737</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36037</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40689</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>72111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79896</t>
+          <t>79781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>34387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52416</t>
+          <t>52763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58674</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22278</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36967</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54996</t>
+          <t>55193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113010</t>
+          <t>112934</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121618</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127277</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137834</t>
+          <t>137597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244363</t>
+          <t>244198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257097</t>
+          <t>257436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>26651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33745</t>
+          <t>33740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57570</t>
+          <t>58669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>65198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37353</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76374</t>
+          <t>76360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>31351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35384</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58516</t>
+          <t>58704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66303</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41087</t>
+          <t>41089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>42548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81351</t>
+          <t>81403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88131</t>
+          <t>88279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>135791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>143741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145670</t>
+          <t>146094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155281</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285972</t>
+          <t>285950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297460</t>
+          <t>297912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>45053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36053</t>
+          <t>36608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78991</t>
+          <t>79350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23111</t>
+          <t>22914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>27165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>47619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54247</t>
+          <t>54259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>23583</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56014</t>
+          <t>56065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61653</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121790</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>126768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>111647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120221</t>
+          <t>120071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235753</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245858</t>
+          <t>246001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>48140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56967</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62916</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99301</t>
+          <t>99413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106759</t>
+          <t>106654</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72576</t>
+          <t>72682</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52373</t>
+          <t>52558</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128326</t>
+          <t>128180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133687</t>
+          <t>133633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29987</t>
+          <t>29358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58625</t>
+          <t>59405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63755</t>
+          <t>63778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170335</t>
+          <t>169891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176942</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170272</t>
+          <t>170673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>179214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345182</t>
+          <t>344235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>355181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1348</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5065</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4169</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4376</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27263</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24425</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31470</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27753</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28649</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,3%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27263</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>24298</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>86</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>55020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60824</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5262</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4258</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8405</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8159</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5245</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39378</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36044</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40689</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37389</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33242</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39860</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>33488</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39819</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39378</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36061</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40685</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72111</t>
+          <t>72002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79781</t>
+          <t>79881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6329</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>981</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3621</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2814</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7081</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32309</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28794</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34399</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>24183</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21800</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>21543</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32309</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28042</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34387</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,99%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>90</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58854</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4311</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8746</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3842</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4311</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8945</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34506</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30071</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>37244</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24989</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22149</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21835</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,04%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>34506</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>29872</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>36884</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,89%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>76,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>83</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55193</t>
+          <t>54459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>62284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6438</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16150</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4042</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12371</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12252</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6322</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17167</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133454</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>127769</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137481</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118030</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112934</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121263</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113053</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121407</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>133454</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>126752</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>137597</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244198</t>
+          <t>243989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257436</t>
+          <t>257337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,92 +2670,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6712</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2605</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7773</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31819</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27712</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33747</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31819</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26651</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>33740</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58669</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65198</t>
+          <t>65196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,102 +3018,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3797</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3028</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4644</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4984</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39645</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40277</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37996</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37324</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39645</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36871</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>116</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76360</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5245</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3664</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1613</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7282</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7376</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5061</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34092</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30749</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35383</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>29300</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25682</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31351</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25588</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>31548</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34092</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30933</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35387</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,72%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58704</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4883</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2153</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5674</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5699</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4681</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46342</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42346</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>39633</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36112</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41089</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>36087</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41080</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>46342</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>42548</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81403</t>
+          <t>81171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88279</t>
+          <t>88271</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11462</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11430</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11801</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11872</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>151896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>146504</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155326</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>140657</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>135791</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143741</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>135420</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>143879</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>151896</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>146094</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>155050</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285950</t>
+          <t>286011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297912</t>
+          <t>297183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3063</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>677</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3505</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3483</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23499</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21113</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23499</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20671</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>64</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45053</t>
+          <t>44983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,107 +4960,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5384</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1410</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4496</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39737</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35763</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39737</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36608</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>88,97%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>128</t>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79350</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1675</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4701</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4489</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22716</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25940</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22914</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27165</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23044</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27164</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,94%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>83,45%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>26327</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>23317</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>48521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54259</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2925</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6563</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27502</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29466</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32083</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29863</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>29125</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27502</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23583</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>29511</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>78,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>81</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56065</t>
+          <t>55552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>61659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11480</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5733</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11629</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117066</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111796</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>120178</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>125081</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>121728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>126768</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>121907</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>126755</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117066</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>111647</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>120071</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236650</t>
+          <t>236501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>246375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1784</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5470</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2193</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>19,77%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5361</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24230</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22838</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>26308</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26543</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22190</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27660</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>80,23%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>82</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>48736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2692</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6652</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3451</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2849</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53766</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49806</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>55621</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>43301</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>39859</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>35491</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32685</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36136</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>60960</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>56877</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>62959</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>89,14%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>147</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104262</t>
+          <t>89257</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99413</t>
+          <t>84945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106654</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4656</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1188</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4389</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4582</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4365</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51448</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47699</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>75883</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72682</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>49645</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46244</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>50826</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,98%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>56055</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52558</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>56923</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>144</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>131938</t>
+          <t>101094</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>96971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133633</t>
+          <t>102792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,69 +7593,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3817</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3914</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1247</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4451</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>13,17%</t>
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30338</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>29793</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26317</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28956</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25809</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>29723</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>32562</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>29358</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>33809</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>90</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>62355</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63778</t>
+          <t>60664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7824</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>159783</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>154774</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>162512</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>174819</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>169891</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>176897</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>176120</t>
+          <t>140400</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170673</t>
+          <t>136107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179214</t>
+          <t>142229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>350939</t>
+          <t>300183</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>344235</t>
+          <t>293932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
